--- a/raw/D7.xlsx
+++ b/raw/D7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A_Shaikhiev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B682BCB-C0B4-4C65-B50F-037A5CFF6334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6F2112-6F06-472A-9A47-FE3F0F9CFDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,8 @@
     <sheet name="12." sheetId="24" r:id="rId24"/>
     <sheet name="13." sheetId="25" r:id="rId25"/>
     <sheet name="14." sheetId="26" r:id="rId26"/>
+    <sheet name="15." sheetId="27" r:id="rId27"/>
+    <sheet name="16." sheetId="28" r:id="rId28"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -736,6 +738,78 @@
 </comments>
 </file>
 
+<file path=xl/comments27.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{60303214-0E0E-4D43-A8DA-FB0B4970DA6E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments28.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{75F5982D-D227-4B23-A2AE-F3778E0FA110}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -989,7 +1063,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2519" uniqueCount="175">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2415,7 +2489,67 @@
     <cellStyle name="Обычный 2 2 10" xfId="5" xr:uid="{3C0E49EE-7F4E-45BB-8ABA-96738A2695D3}"/>
     <cellStyle name="Процентный 2" xfId="7" xr:uid="{2520827D-32CF-42EF-9128-E28B686D603C}"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="84">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4819,13 +4953,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6169,13 +6303,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7520,13 +7654,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8873,13 +9007,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10226,13 +10360,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11581,13 +11715,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12934,13 +13068,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14286,13 +14420,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15632,13 +15766,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16978,13 +17112,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18324,13 +18458,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19685,13 +19819,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21031,13 +21165,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22376,13 +22510,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23724,13 +23858,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25070,13 +25204,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26416,13 +26550,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27761,13 +27895,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28541,6 +28675,2696 @@
       <c r="E52" s="73"/>
       <c r="F52" s="72" t="s">
         <v>173</v>
+      </c>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="49"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="49"/>
+      <c r="E56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="G57" s="73"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G58" s="71"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="86"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="92"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="95"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="14"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="14"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="65"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="65"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="65"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="65"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="36"/>
+      <c r="C78" s="97"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="97"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="65"/>
+      <c r="B83" s="93"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="97"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="85"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="91"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="102"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="86"/>
+      <c r="B88" s="102"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="86"/>
+      <c r="B89" s="102"/>
+      <c r="C89" s="86"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="17"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="94"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="92"/>
+      <c r="B91" s="102"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="95"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="14"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="36"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="104"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="105"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="36"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="106"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="107"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G94:H95" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G93:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G86:G88 G89:H92 H85:H88" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A67E928-5E4E-42A5-9E37-4A63073CAD2C}">
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="27"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="C10" s="35"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="37"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="35"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="22"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="35"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="35"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="65"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="65"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="58"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+      <c r="B39" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="14"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="65"/>
+      <c r="B40" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="7"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="65"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="74"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="68"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="69"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="49"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="71"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="65"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="71"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="G50" s="77"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="73"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="65"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="49"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="49"/>
+      <c r="E56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="G57" s="73"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G58" s="71"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="86"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="92"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="95"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="14"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="14"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="65"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="65"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="65"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="65"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="36"/>
+      <c r="C78" s="97"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="97"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="65"/>
+      <c r="B83" s="93"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="97"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="85"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="91"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="102"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="86"/>
+      <c r="B88" s="102"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="86"/>
+      <c r="B89" s="102"/>
+      <c r="C89" s="86"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="17"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="94"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="92"/>
+      <c r="B91" s="102"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="95"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="14"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="36"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="104"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="105"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="36"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="106"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="107"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G94:H95" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G93:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G86:G88 G89:H92 H85:H88" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D190A7B-05A2-41F7-8C27-0069179A8102}">
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="110" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="27"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="C10" s="35"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="37"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="35"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="22"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="111" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="110" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="35"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="35"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="65"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="65"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="58"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+      <c r="B39" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="14"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="65"/>
+      <c r="B40" s="62" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="7"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="65"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="74"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="68"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="69"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="49"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="71"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="65"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="71"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="G50" s="77"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="73"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="65"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="72" t="s">
+        <v>79</v>
       </c>
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
@@ -30465,13 +33289,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31824,13 +34648,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33187,13 +36011,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34547,13 +37371,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35896,13 +38720,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37249,13 +40073,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -38602,13 +41426,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/raw/D7.xlsx
+++ b/raw/D7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A_Shaikhiev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47154355-794C-491F-A606-E01F5EB6BE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA143417-4CFC-4D32-8258-729DC2630B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="4" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -41,6 +41,7 @@
     <sheet name="14." sheetId="26" r:id="rId26"/>
     <sheet name="15." sheetId="27" r:id="rId27"/>
     <sheet name="26." sheetId="28" r:id="rId28"/>
+    <sheet name="27." sheetId="29" r:id="rId29"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -810,6 +811,42 @@
 </comments>
 </file>
 
+<file path=xl/comments29.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{EB1079A8-4E7D-4A28-AB65-C13D801D2276}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1063,7 +1100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2518" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="177">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2495,7 +2532,37 @@
     <cellStyle name="Обычный 2 2 10" xfId="5" xr:uid="{3C0E49EE-7F4E-45BB-8ABA-96738A2695D3}"/>
     <cellStyle name="Процентный 2" xfId="7" xr:uid="{2520827D-32CF-42EF-9128-E28B686D603C}"/>
   </cellStyles>
-  <dxfs count="84">
+  <dxfs count="87">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4959,13 +5026,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6309,13 +6376,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7660,13 +7727,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9013,13 +9080,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10366,13 +10433,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11721,13 +11788,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13074,13 +13141,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14426,13 +14493,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15772,13 +15839,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17118,13 +17185,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18464,13 +18531,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19825,13 +19892,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21171,13 +21238,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22516,13 +22583,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23864,13 +23931,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25210,13 +25277,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26556,13 +26623,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27901,13 +27968,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29246,13 +29313,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30591,13 +30658,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30673,6 +30740,1348 @@
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="14"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="27"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="C10" s="35"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="37"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="35"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="22"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="119" t="s">
+        <v>152</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="35"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="35"/>
+      <c r="G35" s="65"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="65"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="58"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+      <c r="B39" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="65"/>
+      <c r="C40" s="122" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="7"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="65"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="68"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="69"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="49"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="71"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="65"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="71"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="77"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="73"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="65"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="49"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="49"/>
+      <c r="E56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="73"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="85"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="86"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="92"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="95"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="14"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="14"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="65"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="65"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="65"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="65"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="36"/>
+      <c r="C78" s="97"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="97"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="65"/>
+      <c r="B83" s="93"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="97"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="85"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="91"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="102"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="86"/>
+      <c r="B88" s="102"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="86"/>
+      <c r="B89" s="102"/>
+      <c r="C89" s="86"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="17"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="94"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="92"/>
+      <c r="B91" s="102"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="95"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="14"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="36"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="104"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="105"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="36"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="106"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="107"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G94:H95" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G93:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G86:G88 G89:H92 H85:H88" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{074B3048-BA79-46E8-9F2E-E262246B2436}">
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="14"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="9" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
@@ -33292,13 +34701,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34651,13 +36060,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -36014,13 +37423,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37374,13 +38783,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -38723,13 +40132,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -40076,13 +41485,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41429,13 +42838,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/raw/D7.xlsx
+++ b/raw/D7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A_Shaikhiev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA143417-4CFC-4D32-8258-729DC2630B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68036ADB-8A2D-422D-B709-72CA77E22420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="4" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="5" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -42,6 +42,7 @@
     <sheet name="15." sheetId="27" r:id="rId27"/>
     <sheet name="26." sheetId="28" r:id="rId28"/>
     <sheet name="27." sheetId="29" r:id="rId29"/>
+    <sheet name="28." sheetId="30" r:id="rId30"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -883,6 +884,42 @@
 </comments>
 </file>
 
+<file path=xl/comments30.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{5EA9A985-3C74-4773-AE85-4A3A4E504A74}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1100,7 +1137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="178">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -1631,6 +1668,9 @@
   </si>
   <si>
     <t>49-H343912</t>
+  </si>
+  <si>
+    <t>35-H317112д/н</t>
   </si>
 </sst>
 </file>
@@ -2532,7 +2572,37 @@
     <cellStyle name="Обычный 2 2 10" xfId="5" xr:uid="{3C0E49EE-7F4E-45BB-8ABA-96738A2695D3}"/>
     <cellStyle name="Процентный 2" xfId="7" xr:uid="{2520827D-32CF-42EF-9128-E28B686D603C}"/>
   </cellStyles>
-  <dxfs count="87">
+  <dxfs count="90">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5026,13 +5096,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6376,13 +6446,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7727,13 +7797,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9080,13 +9150,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10433,13 +10503,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11788,13 +11858,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13141,13 +13211,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14493,13 +14563,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15839,13 +15909,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17185,13 +17255,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18531,13 +18601,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19892,13 +19962,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21238,13 +21308,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22583,13 +22653,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23931,13 +24001,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25277,13 +25347,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26623,13 +26693,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27968,13 +28038,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29313,13 +29383,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30658,13 +30728,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32000,13 +32070,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33342,13 +33412,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34701,13 +34771,1358 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50772C17-1444-41C9-93DC-F52478708ADE}">
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="14"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="27"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="C10" s="35"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="37"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="35"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="22"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="35"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="119" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="35"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="65"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="35"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="58"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="65"/>
+      <c r="B40" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="65"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="7"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="65"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="112" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="68"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="69"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="49"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="71"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="65"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="71"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="77"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="73"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="65"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="49"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="49"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="73"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="85"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="86"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="92"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="95"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="14"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="14"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="65"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="65"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="65"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="65"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="36"/>
+      <c r="C78" s="97"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="97"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="65"/>
+      <c r="B83" s="93"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="97"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="85"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="91"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="102"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="86"/>
+      <c r="B88" s="102"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="86"/>
+      <c r="B89" s="102"/>
+      <c r="C89" s="86"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="17"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="94"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="92"/>
+      <c r="B91" s="102"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="95"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="14"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="36"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="104"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="105"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="36"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="106"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="107"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G94:H95" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G93:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G86:G88 G89:H92 H85:H88" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -36060,13 +37475,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37423,13 +38838,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -38783,13 +40198,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -40132,13 +41547,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41485,13 +42900,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42838,13 +44253,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/raw/D7.xlsx
+++ b/raw/D7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A_Shaikhiev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68036ADB-8A2D-422D-B709-72CA77E22420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCE7A8B-B195-4102-B245-97422C10B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="5" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="6" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet name="26." sheetId="28" r:id="rId28"/>
     <sheet name="27." sheetId="29" r:id="rId29"/>
     <sheet name="28." sheetId="30" r:id="rId30"/>
+    <sheet name="29." sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -920,6 +921,42 @@
 </comments>
 </file>
 
+<file path=xl/comments31.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{043DB657-354C-4C40-8298-D86F1A4A0BBB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1137,7 +1174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="178">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2572,7 +2609,37 @@
     <cellStyle name="Обычный 2 2 10" xfId="5" xr:uid="{3C0E49EE-7F4E-45BB-8ABA-96738A2695D3}"/>
     <cellStyle name="Процентный 2" xfId="7" xr:uid="{2520827D-32CF-42EF-9128-E28B686D603C}"/>
   </cellStyles>
-  <dxfs count="90">
+  <dxfs count="93">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5096,13 +5163,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6446,13 +6513,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7797,13 +7864,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9150,13 +9217,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10503,13 +10570,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11858,13 +11925,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13211,13 +13278,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14563,13 +14630,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15909,13 +15976,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17255,13 +17322,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18601,13 +18668,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19962,13 +20029,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21308,13 +21375,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22653,13 +22720,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24001,13 +24068,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25347,13 +25414,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26693,13 +26760,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28038,13 +28105,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29383,13 +29450,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30728,13 +30795,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32070,13 +32137,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33412,13 +33479,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34771,13 +34838,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35368,6 +35435,1348 @@
       <c r="A39" s="76" t="s">
         <v>176</v>
       </c>
+      <c r="B39" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="65"/>
+      <c r="B40" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="65"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="7"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="65"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="112" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="68"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="69"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="49"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="71"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="65"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="71"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="77"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="73"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="65"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="49"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="49"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="73"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="85"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="86"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="92"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="95"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="14"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="14"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="65"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="65"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="65"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="65"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="36"/>
+      <c r="C78" s="97"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="97"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="65"/>
+      <c r="B83" s="93"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="97"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="85"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="91"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="102"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="86"/>
+      <c r="B88" s="102"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="86"/>
+      <c r="B89" s="102"/>
+      <c r="C89" s="86"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="17"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="94"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="92"/>
+      <c r="B91" s="102"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="95"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="14"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="36"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="104"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="105"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="36"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="106"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="107"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G94:H95" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G93:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G86:G88 G89:H92 H85:H88" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D63C3E-ED40-4E7E-8F7D-4727ED43BB72}">
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="14"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="27"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="C10" s="35"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="37"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="38"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="35"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="22"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="35"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="119" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="35"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="65"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="35"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="58"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="76"/>
       <c r="B39" s="62" t="s">
         <v>167</v>
       </c>
@@ -37475,13 +38884,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -38838,13 +40247,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -40198,13 +41607,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41547,13 +42956,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42900,13 +44309,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -44253,13 +45662,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/raw/D7.xlsx
+++ b/raw/D7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A_Shaikhiev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCE7A8B-B195-4102-B245-97422C10B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B196EE-0DC3-472A-BA90-CB232EE97F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="6" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="7" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <sheet name="27." sheetId="29" r:id="rId29"/>
     <sheet name="28." sheetId="30" r:id="rId30"/>
     <sheet name="29." sheetId="31" r:id="rId31"/>
+    <sheet name="30." sheetId="32" r:id="rId32"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -957,6 +958,42 @@
 </comments>
 </file>
 
+<file path=xl/comments32.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E80" authorId="0" shapeId="0" xr:uid="{63DF2D79-B611-4BC6-B57E-4DC63F7B06E3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1174,7 +1211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2786" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="178">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -2609,7 +2646,37 @@
     <cellStyle name="Обычный 2 2 10" xfId="5" xr:uid="{3C0E49EE-7F4E-45BB-8ABA-96738A2695D3}"/>
     <cellStyle name="Процентный 2" xfId="7" xr:uid="{2520827D-32CF-42EF-9128-E28B686D603C}"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="96">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5163,13 +5230,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="91" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="90" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6513,13 +6580,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7864,13 +7931,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9217,13 +9284,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10570,13 +10637,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11925,13 +11992,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13278,13 +13345,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14630,13 +14697,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15976,13 +16043,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17322,13 +17389,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18668,13 +18735,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20029,13 +20096,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21375,13 +21442,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22720,13 +22787,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24068,13 +24135,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25414,13 +25481,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26760,13 +26827,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28105,13 +28172,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29450,13 +29517,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30795,13 +30862,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32137,13 +32204,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33479,13 +33546,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34838,13 +34905,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -36183,13 +36250,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37024,6 +37091,1347 @@
       <c r="F56" s="76" t="s">
         <v>133</v>
       </c>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G57" s="73"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="85"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="71"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="86"/>
+      <c r="G63" s="77"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="65"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="85"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="65"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="91"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="86"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="92"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="86"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="86"/>
+      <c r="G69" s="91"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="17"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="94"/>
+      <c r="G70" s="91"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="92"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="93"/>
+      <c r="E71" s="95"/>
+      <c r="F71" s="92"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="14"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="69"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="14"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="93"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="65"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="65"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="65"/>
+      <c r="B76" s="96"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="65"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="73"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B78" s="36"/>
+      <c r="C78" s="97"/>
+      <c r="D78" s="92"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="97"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="96"/>
+      <c r="C79" s="92"/>
+      <c r="D79" s="92"/>
+      <c r="E79" s="97"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="96"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="93"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="65"/>
+      <c r="B83" s="93"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="97"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="85"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="91"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="102"/>
+      <c r="C87" s="65"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="86"/>
+      <c r="B88" s="102"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="73"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="86"/>
+      <c r="B89" s="102"/>
+      <c r="C89" s="86"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="86"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="17"/>
+      <c r="B90" s="102"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="94"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="92"/>
+      <c r="B91" s="102"/>
+      <c r="C91" s="92"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="95"/>
+      <c r="F91" s="92"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="14"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="69"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="36"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="36"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="104"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="105"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="36"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="36"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="106"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="107"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G94:H95" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G93:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G86:G88 G89:H92 H85:H88" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2939EEE6-E2B8-461B-80AB-54457D595127}">
+  <dimension ref="A1:J97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="14"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="27"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="30"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="C10" s="35"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="19"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="37"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="39"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="42"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="35"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="22"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="14"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="14"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="35"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="14"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="14"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="119" t="s">
+        <v>159</v>
+      </c>
+      <c r="G32" s="65"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="35"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="65"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="35"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="53"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="58"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="76"/>
+      <c r="B39" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="61"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="65"/>
+      <c r="B40" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="122" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="7"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="65"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="112" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="64"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G42" s="14"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="68"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="69"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="65"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="65"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="49"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="71"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="65"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" s="71"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" s="77"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="73"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="65"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="49"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D53" s="49"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="49"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="49"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="49"/>
+      <c r="E56" s="73"/>
       <c r="G56" s="73"/>
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
@@ -38884,13 +40292,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -40247,13 +41655,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41607,13 +43015,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42956,13 +44364,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -44309,13 +45717,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -45662,13 +47070,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/raw/D7.xlsx
+++ b/raw/D7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A_Shaikhiev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B196EE-0DC3-472A-BA90-CB232EE97F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA02F295-CE51-48F8-A16A-246D8A55964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="7" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="8" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,7 @@
     <sheet name="28." sheetId="30" r:id="rId30"/>
     <sheet name="29." sheetId="31" r:id="rId31"/>
     <sheet name="30." sheetId="32" r:id="rId32"/>
+    <sheet name="31." sheetId="33" r:id="rId33"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -994,6 +995,42 @@
 </comments>
 </file>
 
+<file path=xl/comments33.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="E85" authorId="0" shapeId="0" xr:uid="{CA693B56-3D4C-4B27-BA19-2604FD93D3F7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>есптен шығуға</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1211,7 +1248,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="183">
   <si>
     <t>ЦДН-1</t>
   </si>
@@ -1746,6 +1783,21 @@
   <si>
     <t>35-H317112д/н</t>
   </si>
+  <si>
+    <t>ЦИТС</t>
+  </si>
+  <si>
+    <t>22-Н363812</t>
+  </si>
+  <si>
+    <t>28-H321412</t>
+  </si>
+  <si>
+    <t>28-H314712д</t>
+  </si>
+  <si>
+    <t>28-Н318712</t>
+  </si>
 </sst>
 </file>
 
@@ -2257,7 +2309,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2633,6 +2685,12 @@
     <xf numFmtId="0" fontId="39" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal_Sheet1" xfId="8" xr:uid="{C938A70B-DE1B-41C4-8D61-5F3B74A09223}"/>
@@ -2646,7 +2704,37 @@
     <cellStyle name="Обычный 2 2 10" xfId="5" xr:uid="{3C0E49EE-7F4E-45BB-8ABA-96738A2695D3}"/>
     <cellStyle name="Процентный 2" xfId="7" xr:uid="{2520827D-32CF-42EF-9128-E28B686D603C}"/>
   </cellStyles>
-  <dxfs count="96">
+  <dxfs count="99">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5230,13 +5318,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="93" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6580,13 +6668,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7931,13 +8019,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9284,13 +9372,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10637,13 +10725,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11992,13 +12080,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13345,13 +13433,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14697,13 +14785,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16043,13 +16131,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -17389,13 +17477,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18735,13 +18823,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20096,13 +20184,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="91" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="90" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21442,13 +21530,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22787,13 +22875,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -24135,13 +24223,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -25481,13 +25569,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -26827,13 +26915,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28172,13 +28260,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29517,13 +29605,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30862,13 +30950,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -32204,13 +32292,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33546,13 +33634,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34905,13 +34993,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -36250,13 +36338,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37592,13 +37680,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -38933,12 +39021,1421 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69:C71">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66:C68">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B30C51-8138-4944-9626-813AC2D90413}">
+  <dimension ref="A1:J102"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17" style="8" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="F3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B7" s="10"/>
+      <c r="C7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="129" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="30"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="30"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
+      <c r="C15" s="35"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="35"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="19"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="19"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="19"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="14"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="37"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="124" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="35"/>
+      <c r="F20" s="14"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="38"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="39"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="14"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="31"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="27"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="31"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="22"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="14"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="14"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="14"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="35"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="14"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="14"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="49"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="14"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="119" t="s">
+        <v>159</v>
+      </c>
+      <c r="G37" s="65"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="14"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="14"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="65"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="35"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="35"/>
+      <c r="G40" s="65"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" s="53"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="35"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="58"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="76"/>
+      <c r="B44" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C44" s="115" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="61"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="65"/>
+      <c r="B45" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" s="122" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="60"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="30"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="7"/>
+      <c r="B46" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" s="65"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="130" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" s="14"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G47" s="14"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="68"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="65"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="112" t="s">
+        <v>121</v>
+      </c>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="69"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="65"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="65"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="65"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G50" s="65"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="49"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B52" s="64"/>
+      <c r="C52" s="65"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="112" t="s">
+        <v>115</v>
+      </c>
+      <c r="G52" s="71"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="65"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="65"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="65"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="65"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="129" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" s="77"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="65"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G56" s="73"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="65"/>
+      <c r="B57" s="74"/>
+      <c r="C57" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" s="49"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="65"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="65"/>
+      <c r="B59" s="74"/>
+      <c r="C59" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" s="49"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="65"/>
+      <c r="B60" s="74"/>
+      <c r="C60" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="49"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="65"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="49"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="65"/>
+      <c r="B62" s="74"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="G62" s="73"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="65"/>
+      <c r="B63" s="82"/>
+      <c r="C63" s="83"/>
+      <c r="D63" s="84"/>
+      <c r="E63" s="85"/>
+      <c r="G63" s="71"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="71"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="65"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="83"/>
+      <c r="E65" s="86"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="65"/>
+      <c r="B66" s="82"/>
+      <c r="C66" s="82"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="73"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="65"/>
+      <c r="B67" s="82"/>
+      <c r="C67" s="82"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="65"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="87"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="88"/>
+      <c r="F68" s="86"/>
+      <c r="G68" s="77"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="65"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="87"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="65"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="89"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="65"/>
+      <c r="B70" s="82"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="85"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="65"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="65"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="91"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="65"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="90"/>
+      <c r="D72" s="92"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="91"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="86"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="90"/>
+      <c r="D73" s="92"/>
+      <c r="E73" s="73"/>
+      <c r="F73" s="73"/>
+      <c r="G73" s="91"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="86"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="90"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="86"/>
+      <c r="G74" s="91"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="17"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="90"/>
+      <c r="D75" s="93"/>
+      <c r="E75" s="66"/>
+      <c r="F75" s="94"/>
+      <c r="G75" s="91"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="92"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="90"/>
+      <c r="D76" s="93"/>
+      <c r="E76" s="95"/>
+      <c r="F76" s="92"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="14"/>
+      <c r="B77" s="82"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="93"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="69"/>
+      <c r="G77" s="91"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" s="14"/>
+      <c r="B78" s="82"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="93"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="65"/>
+      <c r="B79" s="82"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="93"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="65"/>
+      <c r="B80" s="82"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="93"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="71"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="65"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="93"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="73"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="65"/>
+      <c r="B82" s="96"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="93"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B83" s="36"/>
+      <c r="C83" s="97"/>
+      <c r="D83" s="92"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="97"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="65"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="92"/>
+      <c r="D84" s="92"/>
+      <c r="E84" s="97"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="71"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="65"/>
+      <c r="B85" s="96"/>
+      <c r="C85" s="92"/>
+      <c r="D85" s="92"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="73"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" s="65"/>
+      <c r="B86" s="98"/>
+      <c r="C86" s="92"/>
+      <c r="D86" s="92"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="71"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="65"/>
+      <c r="B87" s="93"/>
+      <c r="C87" s="99"/>
+      <c r="D87" s="100"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="73"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="65"/>
+      <c r="B88" s="93"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="86"/>
+      <c r="G88" s="77"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="65"/>
+      <c r="B89" s="93"/>
+      <c r="C89" s="99"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="86"/>
+      <c r="F89" s="49"/>
+      <c r="G89" s="101"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="65"/>
+      <c r="B90" s="93"/>
+      <c r="C90" s="99"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="49"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="97"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="65"/>
+      <c r="B91" s="85"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="49"/>
+      <c r="F91" s="49"/>
+      <c r="G91" s="91"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="65"/>
+      <c r="B92" s="102"/>
+      <c r="C92" s="65"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="49"/>
+      <c r="F92" s="49"/>
+      <c r="G92" s="91"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="86"/>
+      <c r="B93" s="102"/>
+      <c r="C93" s="86"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="73"/>
+      <c r="F93" s="73"/>
+      <c r="G93" s="91"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="14"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" s="86"/>
+      <c r="B94" s="102"/>
+      <c r="C94" s="86"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="49"/>
+      <c r="F94" s="86"/>
+      <c r="G94" s="91"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="14"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="17"/>
+      <c r="B95" s="102"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="66"/>
+      <c r="F95" s="94"/>
+      <c r="G95" s="91"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="14"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="92"/>
+      <c r="B96" s="102"/>
+      <c r="C96" s="92"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="95"/>
+      <c r="F96" s="92"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="14"/>
+      <c r="B97" s="102"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="69"/>
+      <c r="G97" s="91"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" s="36"/>
+      <c r="B98" s="103"/>
+      <c r="C98" s="36"/>
+      <c r="D98" s="36"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="36"/>
+      <c r="G98" s="36"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="36"/>
+      <c r="J98" s="36"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" s="104"/>
+      <c r="B99" s="103"/>
+      <c r="C99" s="104"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="105"/>
+      <c r="F99" s="104"/>
+      <c r="G99" s="36"/>
+      <c r="H99" s="36"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="36"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" s="36"/>
+      <c r="B100" s="103"/>
+      <c r="C100" s="106"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="107"/>
+      <c r="G100" s="108"/>
+      <c r="H100" s="36"/>
+      <c r="I100" s="36"/>
+      <c r="J100" s="36"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A102" s="14"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="14"/>
+    </row>
+  </sheetData>
+  <protectedRanges>
+    <protectedRange sqref="G99:H100" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_3"/>
+    <protectedRange sqref="G98:H98" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_8"/>
+    <protectedRange sqref="G91:G93 G94:H97 H90:H93" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_9"/>
+    <protectedRange sqref="H83:H89" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="D76">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C69:C71">
+  <conditionalFormatting sqref="C74:C76">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C66:C68">
+  <conditionalFormatting sqref="C71:C73">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40292,13 +41789,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41655,13 +43152,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -43015,13 +44512,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -44364,13 +45861,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -45717,13 +47214,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -47070,13 +48567,13 @@
     <protectedRange sqref="H78:H84" name="Range1_1_1_1_1_1_1_1_1_1_3_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_2_3_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_2_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_1_10"/>
   </protectedRanges>
   <conditionalFormatting sqref="D71">
-    <cfRule type="duplicateValues" dxfId="71" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C69:C71">
-    <cfRule type="duplicateValues" dxfId="70" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66:C68">
-    <cfRule type="duplicateValues" dxfId="69" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
